--- a/terminology/ValueSet-referralorder-types.xlsx
+++ b/terminology/ValueSet-referralorder-types.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -49,7 +49,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -94,7 +94,9 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>This material contains content from LOINC (http://loinc.org). LOINC is copyright © 1995-2020, Regenstrief Institute, Inc. and the Logical Observation Identifiers Names and Codes (LOINC) Committee and is available at no cost under the license at http://loinc.org/license. LOINC® is a registered United States trademark of Regenstrief Institute, Inc</t>
+    <t>This value set includes content from SNOMED CT and LOINC.
+SNOMED CT is copyright © 2002+ International Health Terminology Standards Development Organisation (IHTSDO), and distributed by agreement between IHTSDO and HL7. Implementer use of SNOMED CT is not covered by this agreement
+LOINC is copyright © 1995-2020, Regenstrief Institute, Inc. and the Logical Observation Identifiers Names and Codes (LOINC) Committee and is available at no cost under the license at http://loinc.org/license. LOINC® is a registered United States trademark of Regenstrief Institute, Inc</t>
   </si>
   <si>
     <t>Immutable</t>
